--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -1,136 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\자동생성\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12228"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12228" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>NO.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS-code</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRESS TOOL FOR BRKT-DR SCUFF MTG NO.1/NO.2,LH OF PNL ASSY-S/SILL INR COMPL, LH/RH CONSISTS OF BL FOR BC4i MODEL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Category</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRESS TOOL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CHECKING FIXTURE FOR PLATE-FR BUMPER CRASH BOX, LH OF BEAM COMPL-FR BUMPER FOR BC4i MODEL</t>
-  </si>
-  <si>
-    <t>CHECKING FIXTURE</t>
-  </si>
-  <si>
-    <t>JIG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>W15 FRT L/ARM REINF WELDING JIG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="13"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981048"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -160,35 +107,39 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 59" xfId="1"/>
     <cellStyle name="표준 2" xfId="2"/>
-    <cellStyle name="표준 59" xfId="1"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -253,14 +204,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -526,90 +537,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:D6"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A3:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col min="2" max="2" width="21.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="134.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.796875" customWidth="1"/>
+    <col width="21.8984375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="134.296875" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="13.796875" customWidth="1" style="5" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20.4" customHeight="1" s="5">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>PRESS TOOL</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PRESS TOOL FOR BRKT-DR SCUFF MTG NO.1/NO.2,LH OF PNL ASSY-S/SILL INR COMPL, LH/RH CONSISTS OF BL FOR BC4i MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20.4" customHeight="1" s="5">
+      <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE FOR PLATE-FR BUMPER CRASH BOX, LH OF BEAM COMPL-FR BUMPER FOR BC4i MODEL</t>
+        </is>
+      </c>
     </row>
-    <row r="4" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="6" ht="20.4" customHeight="1" s="5">
+      <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="3">
-        <v>8207.2999999999993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3">
-        <v>9031.7999999999993</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3">
-        <v>8466.2999999999993</v>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>JIG</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>W15 FRT L/ARM REINF WELDING JIG</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C6">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C4">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" priority="8" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+    <cfRule type="duplicateValues" priority="9" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -141,7 +141,77 @@
     <cellStyle name="표준 59" xfId="1"/>
     <cellStyle name="표준 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -542,12 +612,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:C6"/>
+  <dimension ref="A3:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="21.8984375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="134.296875" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="13.796875" customWidth="1" style="5" min="4" max="4"/>
+    <col width="27.296875" customWidth="1" style="5" min="2" max="2"/>
+    <col width="21.8984375" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="134.296875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -558,10 +628,15 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>INV NO</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -571,14 +646,19 @@
       <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>HS2026-05-302P</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>PRESS TOOL</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>PRESS TOOL FOR BRKT-DR SCUFF MTG NO.1/NO.2,LH OF PNL ASSY-S/SILL INR COMPL, LH/RH CONSISTS OF BL FOR BC4i MODEL</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PRESS TOOL FOR BRKT HORN OF BEAM COMPL-FR BUMPER CONSISTS OF PI FOR BC4i MODEL</t>
         </is>
       </c>
     </row>
@@ -586,14 +666,19 @@
       <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>HS2026-05-302P</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>CHECKING FIXTURE</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>CHECKING FIXTURE FOR PLATE-FR BUMPER CRASH BOX, LH OF BEAM COMPL-FR BUMPER FOR BC4i MODEL</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE FOR BRKT-DR SCUFF MTG NO.2,LH OF PNL ASSY-S/SILL INR COMPL, LH/RH FOR BC4i MODEL</t>
         </is>
       </c>
     </row>
@@ -601,29 +686,707 @@
       <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>JIG</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>W15 FRT L/ARM REINF WELDING JIG</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>HS2026-05-302P</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE FOR BRKT-CTR DR SCUFF MTG,LH OF PNL ASSY-S/SILL INR COMPL, LH/RH FOR BC4i MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20.4" customHeight="1" s="5">
+      <c r="A7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HS2026-05-302P</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE FOR BRKT-FR SEAT RR OTR MTG,LH OF PNL &amp; MBR ASSY CTR FLR COMPL (RHD/LHD) FOR BC4i MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20.4" customHeight="1" s="5">
+      <c r="A8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>HS2026-05-302P</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>CHECKING FIXTURE FOR REINF-PARKING BRAKE LEVER MTG RHD OF PNL &amp; MBR ASSY CTR FLR COMPL (RHD/LHD) FOR BC4i MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20.4" customHeight="1" s="5">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="20.4" customHeight="1" s="5">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="20.4" customHeight="1" s="5">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="20.4" customHeight="1" s="5">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="20.4" customHeight="1" s="5">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="20.4" customHeight="1" s="5">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="20.4" customHeight="1" s="5">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="20.4" customHeight="1" s="5">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="20.4" customHeight="1" s="5">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="20.4" customHeight="1" s="5">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="20.4" customHeight="1" s="5">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="20.4" customHeight="1" s="5">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="20.4" customHeight="1" s="5">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="20.4" customHeight="1" s="5">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20.4" customHeight="1" s="5">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="20.4" customHeight="1" s="5">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="20.4" customHeight="1" s="5">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="20.4" customHeight="1" s="5">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="20.4" customHeight="1" s="5">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="20.4" customHeight="1" s="5">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="20.4" customHeight="1" s="5">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="20.4" customHeight="1" s="5">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="20.4" customHeight="1" s="5">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="20.4" customHeight="1" s="5">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="20.4" customHeight="1" s="5">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="20.4" customHeight="1" s="5">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="20.4" customHeight="1" s="5">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="20.4" customHeight="1" s="5">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="20.4" customHeight="1" s="5">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="20.4" customHeight="1" s="5">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="20.4" customHeight="1" s="5">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="20.4" customHeight="1" s="5">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="20.4" customHeight="1" s="5">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="20.4" customHeight="1" s="5">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="20.4" customHeight="1" s="5">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="4" t="n"/>
+    </row>
+    <row r="44" ht="20.4" customHeight="1" s="5">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="20.4" customHeight="1" s="5">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="20.4" customHeight="1" s="5">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="20.4" customHeight="1" s="5">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="4" t="n"/>
+    </row>
+    <row r="48" ht="20.4" customHeight="1" s="5">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="4" t="n"/>
+    </row>
+    <row r="49" ht="20.4" customHeight="1" s="5">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="4" t="n"/>
+    </row>
+    <row r="50" ht="20.4" customHeight="1" s="5">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="4" t="n"/>
+    </row>
+    <row r="51" ht="20.4" customHeight="1" s="5">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="4" t="n"/>
+    </row>
+    <row r="52" ht="20.4" customHeight="1" s="5">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="4" t="n"/>
+    </row>
+    <row r="53" ht="20.4" customHeight="1" s="5">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="4" t="n"/>
+    </row>
+    <row r="54" ht="20.4" customHeight="1" s="5">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="4" t="n"/>
+    </row>
+    <row r="55" ht="20.4" customHeight="1" s="5">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="4" t="n"/>
+    </row>
+    <row r="56" ht="20.4" customHeight="1" s="5">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="4" t="n"/>
+    </row>
+    <row r="57" ht="20.4" customHeight="1" s="5">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="4" t="n"/>
+    </row>
+    <row r="58" ht="20.4" customHeight="1" s="5">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="4" t="n"/>
+    </row>
+    <row r="59" ht="20.4" customHeight="1" s="5">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="4" t="n"/>
+    </row>
+    <row r="60" ht="20.4" customHeight="1" s="5">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="4" t="n"/>
+    </row>
+    <row r="61" ht="20.4" customHeight="1" s="5">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="4" t="n"/>
+    </row>
+    <row r="62" ht="20.4" customHeight="1" s="5">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="4" t="n"/>
+    </row>
+    <row r="63" ht="20.4" customHeight="1" s="5">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="4" t="n"/>
+    </row>
+    <row r="64" ht="20.4" customHeight="1" s="5">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="4" t="n"/>
+    </row>
+    <row r="65" ht="20.4" customHeight="1" s="5">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="4" t="n"/>
+    </row>
+    <row r="66" ht="20.4" customHeight="1" s="5">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="4" t="n"/>
+    </row>
+    <row r="67" ht="20.4" customHeight="1" s="5">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="4" t="n"/>
+    </row>
+    <row r="68" ht="20.4" customHeight="1" s="5">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="4" t="n"/>
+    </row>
+    <row r="69" ht="20.4" customHeight="1" s="5">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="4" t="n"/>
+    </row>
+    <row r="70" ht="20.4" customHeight="1" s="5">
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="4" t="n"/>
+    </row>
+    <row r="71" ht="20.4" customHeight="1" s="5">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="20.4" customHeight="1" s="5">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="20.4" customHeight="1" s="5">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="20.4" customHeight="1" s="5">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="4" t="n"/>
+    </row>
+    <row r="75" ht="20.4" customHeight="1" s="5">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="20.4" customHeight="1" s="5">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="4" t="n"/>
+    </row>
+    <row r="77" ht="20.4" customHeight="1" s="5">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="4" t="n"/>
+    </row>
+    <row r="78" ht="20.4" customHeight="1" s="5">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="4" t="n"/>
+    </row>
+    <row r="79" ht="20.4" customHeight="1" s="5">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="4" t="n"/>
+    </row>
+    <row r="80" ht="20.4" customHeight="1" s="5">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="4" t="n"/>
+    </row>
+    <row r="81" ht="20.4" customHeight="1" s="5">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="4" t="n"/>
+    </row>
+    <row r="82" ht="20.4" customHeight="1" s="5">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="4" t="n"/>
+    </row>
+    <row r="83" ht="20.4" customHeight="1" s="5">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="4" t="n"/>
+    </row>
+    <row r="84" ht="20.4" customHeight="1" s="5">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="4" t="n"/>
+    </row>
+    <row r="85" ht="20.4" customHeight="1" s="5">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="4" t="n"/>
+    </row>
+    <row r="86" ht="20.4" customHeight="1" s="5">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="4" t="n"/>
+    </row>
+    <row r="87" ht="20.4" customHeight="1" s="5">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="4" t="n"/>
+    </row>
+    <row r="88" ht="20.4" customHeight="1" s="5">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="4" t="n"/>
+    </row>
+    <row r="89" ht="20.4" customHeight="1" s="5">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="20.4" customHeight="1" s="5">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="4" t="n"/>
+    </row>
+    <row r="91" ht="20.4" customHeight="1" s="5">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="4" t="n"/>
+    </row>
+    <row r="92" ht="20.4" customHeight="1" s="5">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="4" t="n"/>
+    </row>
+    <row r="93" ht="20.4" customHeight="1" s="5">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="4" t="n"/>
+    </row>
+    <row r="94" ht="20.4" customHeight="1" s="5">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="4" t="n"/>
+    </row>
+    <row r="95" ht="20.4" customHeight="1" s="5">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="4" t="n"/>
+    </row>
+    <row r="96" ht="20.4" customHeight="1" s="5">
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="4" t="n"/>
+    </row>
+    <row r="97" ht="20.4" customHeight="1" s="5">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="4" t="n"/>
+    </row>
+    <row r="98" ht="20.4" customHeight="1" s="5">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="4" t="n"/>
+    </row>
+    <row r="99" ht="20.4" customHeight="1" s="5">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="4" t="n"/>
+    </row>
+    <row r="100" ht="20.4" customHeight="1" s="5">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="4" t="n"/>
+    </row>
+    <row r="101" ht="20.4" customHeight="1" s="5">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="4" t="n"/>
+    </row>
+    <row r="102" ht="20.4" customHeight="1" s="5">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="4" t="n"/>
+    </row>
+    <row r="103" ht="20.4" customHeight="1" s="5">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="4" t="n"/>
+    </row>
+    <row r="104" ht="20.4" customHeight="1" s="5">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="4" t="n"/>
+    </row>
+    <row r="105" ht="20.4" customHeight="1" s="5">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="4" t="n"/>
+    </row>
+    <row r="106" ht="20.4" customHeight="1" s="5">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="4" t="n"/>
+    </row>
+    <row r="107" ht="20.4" customHeight="1" s="5">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="4" t="n"/>
+    </row>
+    <row r="108" ht="20.4" customHeight="1" s="5">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="4" t="n"/>
+    </row>
+    <row r="109" ht="20.4" customHeight="1" s="5">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="4" t="n"/>
+    </row>
+    <row r="110" ht="20.4" customHeight="1" s="5">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="4" t="n"/>
+    </row>
+    <row r="111" ht="20.4" customHeight="1" s="5">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="4" t="n"/>
+    </row>
+    <row r="112" ht="20.4" customHeight="1" s="5">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="4" t="n"/>
+    </row>
+    <row r="113" ht="20.4" customHeight="1" s="5">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="4" t="n"/>
+    </row>
+    <row r="114" ht="20.4" customHeight="1" s="5">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="4" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6">
+  <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" priority="15" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D8">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C4">
-    <cfRule type="duplicateValues" priority="8" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="duplicateValues" priority="9" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5">
+  <conditionalFormatting sqref="D9:D114">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
